--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53741E66-7324-4FFF-8D8A-8256CD920E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9191E5-462B-4FC1-B53E-E3215B362E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="730" windowWidth="22930" windowHeight="15410" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="3580" yWindow="650" windowWidth="22930" windowHeight="15410" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="102">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -369,6 +369,10 @@
   </si>
   <si>
     <t>플레이어 전방 범위의 적들에게 (피해량%)의 광역 피해를 주고, 15초 동안 이동 속도와 공격 속도를 15% 감소 시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 전방 범위의 적들에게 (200%)의 광역 피해를 주고, 15초 동안 이동 속도와 공격 속도를 15% 감소 시킵니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2130,7 +2134,7 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -2162,7 +2166,7 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
         <v>38</v>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9191E5-462B-4FC1-B53E-E3215B362E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F97E15-2E73-4A64-AB88-3B126EA3D26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3580" yWindow="650" windowWidth="22930" windowHeight="15410" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="4080" yWindow="1000" windowWidth="18540" windowHeight="15410" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>cost</t>
   </si>
   <si>
-    <t>effectTarget</t>
-  </si>
-  <si>
     <t>statType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -373,6 +370,10 @@
   </si>
   <si>
     <t>플레이어 전방 범위의 적들에게 (200%)의 광역 피해를 주고, 15초 동안 이동 속도와 공격 속도를 15% 감소 시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectTarget</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -798,16 +799,16 @@
         <v>8010001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" s="2">
         <v>3</v>
@@ -818,16 +819,16 @@
         <v>8010002</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F3" s="2">
         <v>5</v>
@@ -838,16 +839,16 @@
         <v>8010003</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
@@ -858,16 +859,16 @@
         <v>8010004</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2">
         <v>10</v>
@@ -878,16 +879,16 @@
         <v>8010005</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2">
         <v>15</v>
@@ -942,16 +943,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
       <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
         <v>49</v>
-      </c>
-      <c r="H1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
@@ -959,22 +960,22 @@
         <v>80200011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
         <v>45</v>
       </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
@@ -985,22 +986,22 @@
         <v>80200012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2">
         <v>10</v>
@@ -1016,22 +1017,22 @@
         <v>80200013</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
         <v>45</v>
       </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2">
         <v>15</v>
@@ -1047,22 +1048,22 @@
         <v>80200014</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2">
         <v>20</v>
@@ -1078,22 +1079,22 @@
         <v>80200015</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
         <v>45</v>
       </c>
-      <c r="E6" t="s">
-        <v>46</v>
-      </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H6" s="2">
         <v>25</v>
@@ -1109,22 +1110,22 @@
         <v>80200021</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
         <v>45</v>
       </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2">
         <v>5</v>
@@ -1140,22 +1141,22 @@
         <v>80200022</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
         <v>45</v>
       </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="2">
         <v>10</v>
@@ -1171,22 +1172,22 @@
         <v>80200023</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H9" s="2">
         <v>15</v>
@@ -1202,22 +1203,22 @@
         <v>80200024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H10" s="2">
         <v>20</v>
@@ -1233,22 +1234,22 @@
         <v>80200025</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
         <v>45</v>
       </c>
-      <c r="E11" t="s">
-        <v>46</v>
-      </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" s="2">
         <v>25</v>
@@ -1264,22 +1265,22 @@
         <v>80200031</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
         <v>45</v>
       </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2">
         <v>5</v>
@@ -1295,22 +1296,22 @@
         <v>80200032</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
         <v>45</v>
       </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" s="2">
         <v>10</v>
@@ -1326,22 +1327,22 @@
         <v>80200033</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H14" s="2">
         <v>15</v>
@@ -1352,22 +1353,22 @@
         <v>80200034</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
         <v>45</v>
       </c>
-      <c r="E15" t="s">
-        <v>46</v>
-      </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H15" s="2">
         <v>20</v>
@@ -1378,22 +1379,22 @@
         <v>80200035</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2">
         <v>25</v>
@@ -1404,22 +1405,22 @@
         <v>80200041</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2">
         <v>10</v>
@@ -1430,22 +1431,22 @@
         <v>80200042</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="2">
         <v>20</v>
@@ -1456,22 +1457,22 @@
         <v>80200043</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>45</v>
       </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
@@ -1482,22 +1483,22 @@
         <v>80200044</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>45</v>
       </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H20" s="2">
         <v>40</v>
@@ -1508,22 +1509,22 @@
         <v>80200045</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>45</v>
       </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2">
         <v>50</v>
@@ -1534,22 +1535,22 @@
         <v>80200051</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2">
         <v>5</v>
@@ -1560,22 +1561,22 @@
         <v>80200052</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H23" s="2">
         <v>10</v>
@@ -1586,22 +1587,22 @@
         <v>80200053</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H24" s="2">
         <v>15</v>
@@ -1612,22 +1613,22 @@
         <v>80200054</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H25" s="2">
         <v>20</v>
@@ -1638,22 +1639,22 @@
         <v>80200055</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H26" s="2">
         <v>25</v>
@@ -1664,22 +1665,22 @@
         <v>80200061</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2">
         <v>5</v>
@@ -1690,22 +1691,22 @@
         <v>80200062</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H28" s="2">
         <v>10</v>
@@ -1716,22 +1717,22 @@
         <v>80200063</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2">
         <v>15</v>
@@ -1742,22 +1743,22 @@
         <v>80200064</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H30" s="2">
         <v>20</v>
@@ -1768,22 +1769,22 @@
         <v>80200065</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H31" s="2">
         <v>25</v>
@@ -1794,22 +1795,22 @@
         <v>80200071</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2">
         <v>5</v>
@@ -1820,22 +1821,22 @@
         <v>80200072</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H33" s="2">
         <v>10</v>
@@ -1846,22 +1847,22 @@
         <v>80200073</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2">
         <v>15</v>
@@ -1872,22 +1873,22 @@
         <v>80200074</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H35" s="2">
         <v>20</v>
@@ -1898,22 +1899,22 @@
         <v>80200075</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H36" s="2">
         <v>25</v>
@@ -1924,22 +1925,22 @@
         <v>80200081</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2">
         <v>5</v>
@@ -1950,22 +1951,22 @@
         <v>80200082</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H38" s="2">
         <v>10</v>
@@ -1976,22 +1977,22 @@
         <v>80200083</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H39" s="2">
         <v>15</v>
@@ -2002,22 +2003,22 @@
         <v>80200084</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H40" s="2">
         <v>20</v>
@@ -2028,22 +2029,22 @@
         <v>80200085</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H41" s="2">
         <v>25</v>
@@ -2090,40 +2091,40 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>18</v>
-      </c>
-      <c r="P1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="34" x14ac:dyDescent="0.45">
@@ -2131,13 +2132,13 @@
         <v>8010001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2163,13 +2164,13 @@
         <v>8010001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2195,13 +2196,13 @@
         <v>8010001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2230,13 +2231,13 @@
         <v>8010001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2265,13 +2266,13 @@
         <v>8010001</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -2300,13 +2301,13 @@
         <v>8010001</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2335,13 +2336,13 @@
         <v>8010001</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2370,13 +2371,13 @@
         <v>8010001</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -2405,13 +2406,13 @@
         <v>8010001</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2440,13 +2441,13 @@
         <v>8010002</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2472,13 +2473,13 @@
         <v>8010002</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -2504,13 +2505,13 @@
         <v>8010002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -2539,13 +2540,13 @@
         <v>8010002</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -2574,13 +2575,13 @@
         <v>8010002</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -2609,13 +2610,13 @@
         <v>8010002</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2644,13 +2645,13 @@
         <v>8010002</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -2679,13 +2680,13 @@
         <v>8010002</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -2714,13 +2715,13 @@
         <v>8010002</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2749,13 +2750,13 @@
         <v>8010003</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2784,13 +2785,13 @@
         <v>8010003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2819,13 +2820,13 @@
         <v>8010003</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -2857,13 +2858,13 @@
         <v>8010003</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -2895,13 +2896,13 @@
         <v>8010003</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2933,13 +2934,13 @@
         <v>8010003</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2971,13 +2972,13 @@
         <v>8010003</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -3009,13 +3010,13 @@
         <v>8010003</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -3047,13 +3048,13 @@
         <v>8010003</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -3085,13 +3086,13 @@
         <v>8010004</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -3117,13 +3118,13 @@
         <v>8010004</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -3149,13 +3150,13 @@
         <v>8010004</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -3184,13 +3185,13 @@
         <v>8010004</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32">
         <v>4</v>
@@ -3219,13 +3220,13 @@
         <v>8010004</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -3254,13 +3255,13 @@
         <v>8010004</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3289,13 +3290,13 @@
         <v>8010004</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -3324,13 +3325,13 @@
         <v>8010004</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36">
         <v>8</v>
@@ -3359,13 +3360,13 @@
         <v>8010004</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37">
         <v>9</v>
@@ -3394,13 +3395,13 @@
         <v>8010005</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3429,13 +3430,13 @@
         <v>8010005</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -3464,13 +3465,13 @@
         <v>8010005</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -3502,13 +3503,13 @@
         <v>8010005</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -3540,13 +3541,13 @@
         <v>8010005</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>5</v>
@@ -3578,13 +3579,13 @@
         <v>8010005</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -3616,13 +3617,13 @@
         <v>8010005</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E44">
         <v>7</v>
@@ -3654,13 +3655,13 @@
         <v>8010005</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E45">
         <v>8</v>
@@ -3692,13 +3693,13 @@
         <v>8010005</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E46">
         <v>9</v>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F97E15-2E73-4A64-AB88-3B126EA3D26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E2DB1-8CD3-408C-9427-100754E363DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1000" windowWidth="18540" windowHeight="15410" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="5770" yWindow="1870" windowWidth="18540" windowHeight="15410" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E2DB1-8CD3-408C-9427-100754E363DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1F6689-F299-4049-ADE8-D5E7AB021D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5770" yWindow="1870" windowWidth="18540" windowHeight="15410" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="0" yWindow="1360" windowWidth="25350" windowHeight="15410" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="116">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,6 +374,62 @@
   </si>
   <si>
     <t>effectTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconSpritePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Active/Ice_Spirit's_Breath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Active/Thunder_God's_Judgment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Active/Kingdom's_March</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Active/Goddess's_Blessing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Active/Giant's_Tablet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Ancient_King's_Seal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Guardian_Knight's_Cuirass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Wind_Spirit's_Feather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Commander's_Banner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Ancient_Warrior's_Tooth_Necklace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Turtle_Dragon's_Shell_Fragment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Griffin's_Talon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactImages/Passive/Tree_Spirit's_Bark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -758,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C904823C-220B-462B-9A10-524F2CEAD5FF}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -767,14 +823,14 @@
     <col min="4" max="4" width="10.9140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.75" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.08203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,8 +849,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="34" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="34" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>8010001</v>
       </c>
@@ -813,8 +872,11 @@
       <c r="F2" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>8010002</v>
       </c>
@@ -833,8 +895,11 @@
       <c r="F3" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="34" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="34" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>8010003</v>
       </c>
@@ -853,8 +918,11 @@
       <c r="F4" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="34" x14ac:dyDescent="0.45">
+      <c r="G4" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>8010004</v>
       </c>
@@ -873,8 +941,11 @@
       <c r="F5" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>8010005</v>
       </c>
@@ -893,14 +964,17 @@
       <c r="F6" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B9" s="2"/>
     </row>
   </sheetData>
@@ -922,7 +996,7 @@
     <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.08203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -954,6 +1028,9 @@
       <c r="H1" t="s">
         <v>49</v>
       </c>
+      <c r="I1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
@@ -980,6 +1057,9 @@
       <c r="H2" s="2">
         <v>5</v>
       </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="5">
@@ -1006,7 +1086,9 @@
       <c r="H3" s="2">
         <v>10</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" t="s">
+        <v>108</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1037,7 +1119,9 @@
       <c r="H4" s="2">
         <v>15</v>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" t="s">
+        <v>108</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1068,7 +1152,9 @@
       <c r="H5" s="2">
         <v>20</v>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" t="s">
+        <v>108</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1099,7 +1185,9 @@
       <c r="H6" s="2">
         <v>25</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" t="s">
+        <v>108</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1130,7 +1218,9 @@
       <c r="H7" s="2">
         <v>5</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" t="s">
+        <v>109</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1161,7 +1251,9 @@
       <c r="H8" s="2">
         <v>10</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" t="s">
+        <v>109</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1192,7 +1284,9 @@
       <c r="H9" s="2">
         <v>15</v>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" t="s">
+        <v>109</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1223,7 +1317,9 @@
       <c r="H10" s="2">
         <v>20</v>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" t="s">
+        <v>109</v>
+      </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1254,7 +1350,9 @@
       <c r="H11" s="2">
         <v>25</v>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" t="s">
+        <v>109</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1285,7 +1383,9 @@
       <c r="H12" s="2">
         <v>5</v>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1316,7 +1416,9 @@
       <c r="H13" s="2">
         <v>10</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" t="s">
+        <v>110</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1347,6 +1449,9 @@
       <c r="H14" s="2">
         <v>15</v>
       </c>
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="5">
@@ -1373,6 +1478,9 @@
       <c r="H15" s="2">
         <v>20</v>
       </c>
+      <c r="I15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
@@ -1399,8 +1507,11 @@
       <c r="H16" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="5">
         <v>80200041</v>
       </c>
@@ -1425,8 +1536,11 @@
       <c r="H17" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>80200042</v>
       </c>
@@ -1451,8 +1565,11 @@
       <c r="H18" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="5">
         <v>80200043</v>
       </c>
@@ -1477,8 +1594,11 @@
       <c r="H19" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <v>80200044</v>
       </c>
@@ -1503,8 +1623,11 @@
       <c r="H20" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>80200045</v>
       </c>
@@ -1529,8 +1652,11 @@
       <c r="H21" s="2">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>80200051</v>
       </c>
@@ -1555,8 +1681,11 @@
       <c r="H22" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>80200052</v>
       </c>
@@ -1581,8 +1710,11 @@
       <c r="H23" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>80200053</v>
       </c>
@@ -1607,8 +1739,11 @@
       <c r="H24" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>80200054</v>
       </c>
@@ -1633,8 +1768,11 @@
       <c r="H25" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>80200055</v>
       </c>
@@ -1659,8 +1797,11 @@
       <c r="H26" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>80200061</v>
       </c>
@@ -1685,8 +1826,11 @@
       <c r="H27" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>80200062</v>
       </c>
@@ -1711,8 +1855,11 @@
       <c r="H28" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>80200063</v>
       </c>
@@ -1737,8 +1884,11 @@
       <c r="H29" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>80200064</v>
       </c>
@@ -1763,8 +1913,11 @@
       <c r="H30" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>80200065</v>
       </c>
@@ -1789,8 +1942,11 @@
       <c r="H31" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>80200071</v>
       </c>
@@ -1815,8 +1971,11 @@
       <c r="H32" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="5">
         <v>80200072</v>
       </c>
@@ -1841,8 +2000,11 @@
       <c r="H33" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>80200073</v>
       </c>
@@ -1867,8 +2029,11 @@
       <c r="H34" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="5">
         <v>80200074</v>
       </c>
@@ -1893,8 +2058,11 @@
       <c r="H35" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="5">
         <v>80200075</v>
       </c>
@@ -1919,8 +2087,11 @@
       <c r="H36" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="5">
         <v>80200081</v>
       </c>
@@ -1945,8 +2116,11 @@
       <c r="H37" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="5">
         <v>80200082</v>
       </c>
@@ -1971,8 +2145,11 @@
       <c r="H38" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I38" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="5">
         <v>80200083</v>
       </c>
@@ -1997,8 +2174,11 @@
       <c r="H39" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="5">
         <v>80200084</v>
       </c>
@@ -2023,8 +2203,11 @@
       <c r="H40" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" s="5">
         <v>80200085</v>
       </c>
@@ -2048,6 +2231,9 @@
       </c>
       <c r="H41" s="2">
         <v>25</v>
+      </c>
+      <c r="I41" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1F6689-F299-4049-ADE8-D5E7AB021D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463FBD28-C0D5-49B8-8CC4-A22C02FCABE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1360" windowWidth="25350" windowHeight="15410" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="1395" yWindow="780" windowWidth="9390" windowHeight="11385" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -21,18 +21,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -815,22 +803,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C904823C-220B-462B-9A10-524F2CEAD5FF}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="73.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="73.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="46.75" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +841,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>8010001</v>
       </c>
@@ -876,7 +864,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>8010002</v>
       </c>
@@ -899,7 +887,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="34" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>8010003</v>
       </c>
@@ -922,7 +910,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="34" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>8010004</v>
       </c>
@@ -945,7 +933,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>8010005</v>
       </c>
@@ -968,13 +956,13 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
     </row>
   </sheetData>
@@ -987,23 +975,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169A894D-86E5-49E7-834E-05CA49D6DD71}">
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.125" customWidth="1"/>
     <col min="3" max="3" width="35.75" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="51.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1020,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>80200011</v>
       </c>
@@ -1061,7 +1049,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>80200012</v>
       </c>
@@ -1094,7 +1082,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>80200013</v>
       </c>
@@ -1127,7 +1115,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>80200014</v>
       </c>
@@ -1160,7 +1148,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>80200015</v>
       </c>
@@ -1193,7 +1181,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>80200021</v>
       </c>
@@ -1226,7 +1214,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>80200022</v>
       </c>
@@ -1259,7 +1247,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>80200023</v>
       </c>
@@ -1292,7 +1280,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>80200024</v>
       </c>
@@ -1325,7 +1313,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>80200025</v>
       </c>
@@ -1358,7 +1346,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>80200031</v>
       </c>
@@ -1391,7 +1379,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>80200032</v>
       </c>
@@ -1424,7 +1412,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>80200033</v>
       </c>
@@ -1453,7 +1441,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>80200034</v>
       </c>
@@ -1482,7 +1470,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>80200035</v>
       </c>
@@ -1511,7 +1499,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>80200041</v>
       </c>
@@ -1540,7 +1528,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>80200042</v>
       </c>
@@ -1569,7 +1557,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>80200043</v>
       </c>
@@ -1598,7 +1586,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>80200044</v>
       </c>
@@ -1627,7 +1615,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>80200045</v>
       </c>
@@ -1656,7 +1644,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>80200051</v>
       </c>
@@ -1685,7 +1673,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>80200052</v>
       </c>
@@ -1714,7 +1702,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>80200053</v>
       </c>
@@ -1743,7 +1731,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>80200054</v>
       </c>
@@ -1772,7 +1760,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>80200055</v>
       </c>
@@ -1801,7 +1789,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>80200061</v>
       </c>
@@ -1830,7 +1818,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>80200062</v>
       </c>
@@ -1859,7 +1847,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>80200063</v>
       </c>
@@ -1888,7 +1876,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>80200064</v>
       </c>
@@ -1917,7 +1905,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>80200065</v>
       </c>
@@ -1946,7 +1934,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>80200071</v>
       </c>
@@ -1975,7 +1963,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>80200072</v>
       </c>
@@ -2004,7 +1992,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>80200073</v>
       </c>
@@ -2033,7 +2021,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>80200074</v>
       </c>
@@ -2062,7 +2050,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>80200075</v>
       </c>
@@ -2091,7 +2079,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>80200081</v>
       </c>
@@ -2120,7 +2108,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>80200082</v>
       </c>
@@ -2149,7 +2137,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>80200083</v>
       </c>
@@ -2178,7 +2166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>80200084</v>
       </c>
@@ -2207,7 +2195,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>80200085</v>
       </c>
@@ -2246,24 +2234,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F08357B-C30F-4954-99F8-FDAA2158545A}">
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="3" width="57.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.9140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.625" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.58203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2313,7 +2301,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>8010001</v>
       </c>
@@ -2345,7 +2333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>8010001</v>
       </c>
@@ -2377,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>8010001</v>
       </c>
@@ -2412,7 +2400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>8010001</v>
       </c>
@@ -2447,7 +2435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>8010001</v>
       </c>
@@ -2482,7 +2470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>8010001</v>
       </c>
@@ -2517,7 +2505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>8010001</v>
       </c>
@@ -2552,7 +2540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8010001</v>
       </c>
@@ -2587,7 +2575,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8010001</v>
       </c>
@@ -2622,7 +2610,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8010002</v>
       </c>
@@ -2654,7 +2642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>8010002</v>
       </c>
@@ -2686,7 +2674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>8010002</v>
       </c>
@@ -2721,7 +2709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>8010002</v>
       </c>
@@ -2756,7 +2744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>8010002</v>
       </c>
@@ -2791,7 +2779,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>8010002</v>
       </c>
@@ -2826,7 +2814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>8010002</v>
       </c>
@@ -2861,7 +2849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8010002</v>
       </c>
@@ -2896,7 +2884,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>8010002</v>
       </c>
@@ -2931,7 +2919,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>8010003</v>
       </c>
@@ -2966,7 +2954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>8010003</v>
       </c>
@@ -3001,7 +2989,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>8010003</v>
       </c>
@@ -3039,7 +3027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>8010003</v>
       </c>
@@ -3077,7 +3065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>8010003</v>
       </c>
@@ -3115,7 +3103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>8010003</v>
       </c>
@@ -3153,7 +3141,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>8010003</v>
       </c>
@@ -3191,7 +3179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>8010003</v>
       </c>
@@ -3229,7 +3217,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>8010003</v>
       </c>
@@ -3267,7 +3255,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>8010004</v>
       </c>
@@ -3299,7 +3287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>8010004</v>
       </c>
@@ -3331,7 +3319,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>8010004</v>
       </c>
@@ -3366,7 +3354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>8010004</v>
       </c>
@@ -3401,7 +3389,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>8010004</v>
       </c>
@@ -3436,7 +3424,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>8010004</v>
       </c>
@@ -3471,7 +3459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>8010004</v>
       </c>
@@ -3506,7 +3494,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>8010004</v>
       </c>
@@ -3541,7 +3529,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>8010004</v>
       </c>
@@ -3576,7 +3564,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>8010005</v>
       </c>
@@ -3611,7 +3599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>8010005</v>
       </c>
@@ -3646,7 +3634,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>8010005</v>
       </c>
@@ -3684,7 +3672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>8010005</v>
       </c>
@@ -3722,7 +3710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>8010005</v>
       </c>
@@ -3760,7 +3748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>8010005</v>
       </c>
@@ -3798,7 +3786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>8010005</v>
       </c>
@@ -3836,7 +3824,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>8010005</v>
       </c>
@@ -3874,7 +3862,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="34" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>8010005</v>
       </c>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463FBD28-C0D5-49B8-8CC4-A22C02FCABE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BC5586-E1B4-4FF5-970D-D0B9F54E5867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1395" yWindow="780" windowWidth="9390" windowHeight="11385" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BC5586-E1B4-4FF5-970D-D0B9F54E5867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A77D4B-3E02-407A-9FA2-20AE3EA46680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1395" yWindow="780" windowWidth="9390" windowHeight="11385" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A77D4B-3E02-407A-9FA2-20AE3EA46680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FAFFA2-F61D-401F-86D3-D15FE4737D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="780" windowWidth="9390" windowHeight="11385" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FAFFA2-F61D-401F-86D3-D15FE4737D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B2A95D-4E23-4DE0-B6EE-D7A2E24930FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" activeTab="2" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -217,142 +217,6 @@
     <t>AuraRange</t>
   </si>
   <si>
-    <t>플레이어의 공격력을 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 공격력을 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 공격력을 15%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 공격력을 20%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 공격력을 25%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 체력을 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 체력을 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 체력을 15%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 체력을 20%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 체력을 25%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 이동 속도를 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 이동 속도를 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 이동 속도를 15%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 이동 속도를 20%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 이동 속도를 25%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 오라 범위를 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 오라 범위를 20%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 오라 범위를 30%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 오라 범위를 40%로 증가</t>
-  </si>
-  <si>
-    <t>플레이어의 오라 범위를 50%로 증가</t>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 공격력을 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 공격력을 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 공격력을 15%로 증가</t>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 공격력을 20%로 증가</t>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 공격력을 25%로 증가</t>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 체력을 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 체력을 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 체력을 15%로 증가</t>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 체력을 20%로 증가</t>
-  </si>
-  <si>
-    <t>모든 근거리 유닛의 체력을 25%로 증가</t>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 공격력을 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 공격력을 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 공격력을 15%로 증가</t>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 공격력을 20%로 증가</t>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 공격력을 25%로 증가</t>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 체력을 5%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 체력을 10%로 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 체력을 15%로 증가</t>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 체력을 20%로 증가</t>
-  </si>
-  <si>
-    <t>모든 원거리 유닛의 체력을 25%로 증가</t>
-  </si>
-  <si>
     <t>플레이어 전방 범위의 적들에게 (피해량%)의 광역 피해를 주고, 15초 동안 이동 속도와 공격 속도를 15% 감소 시킵니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,6 +282,166 @@
   </si>
   <si>
     <t>ArtifactImages/Passive/Tree_Spirit's_Bark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 공격력 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 공격력 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 공격력 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 공격력 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 공격력 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 체력 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 체력 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 체력 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 체력 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 체력 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 이동 속도 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 이동 속도 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 이동 속도 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 이동 속도 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 이동 속도 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 오라 범위 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 오라 범위 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 오라 범위 30% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 오라 범위 40% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 오라 범위 50% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 공격력 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 공격력 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 공격력 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 공격력 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 공격력 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 체력 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 체력 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 체력 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 체력 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 체력 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 공격력 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 공격력 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 공격력 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 공격력 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 공격력 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 체력 5% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 체력 10% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 체력 15% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 체력 20% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 체력 25% 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -838,7 +862,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -861,7 +885,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -884,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -907,7 +931,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -930,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -953,7 +977,7 @@
         <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1005,7 +1029,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
@@ -1017,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="I1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1028,7 +1052,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>44</v>
@@ -1046,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1057,7 +1081,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
         <v>44</v>
@@ -1075,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1090,7 +1114,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
         <v>44</v>
@@ -1108,7 +1132,7 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1123,7 +1147,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -1141,7 +1165,7 @@
         <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1156,7 +1180,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
@@ -1174,7 +1198,7 @@
         <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1189,7 +1213,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>44</v>
@@ -1207,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1222,7 +1246,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -1240,7 +1264,7 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1255,7 +1279,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>44</v>
@@ -1273,7 +1297,7 @@
         <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1288,7 +1312,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -1306,7 +1330,7 @@
         <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1321,7 +1345,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
@@ -1339,7 +1363,7 @@
         <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1354,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>44</v>
@@ -1372,7 +1396,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -1387,7 +1411,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -1405,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1420,7 +1444,7 @@
         <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>44</v>
@@ -1438,7 +1462,7 @@
         <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1449,7 +1473,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -1467,7 +1491,7 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1478,7 +1502,7 @@
         <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>44</v>
@@ -1496,7 +1520,7 @@
         <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1507,7 +1531,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -1525,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1536,7 +1560,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -1554,7 +1578,7 @@
         <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1565,7 +1589,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
         <v>44</v>
@@ -1583,7 +1607,7 @@
         <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1594,7 +1618,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>44</v>
@@ -1612,7 +1636,7 @@
         <v>40</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1623,7 +1647,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>44</v>
@@ -1641,7 +1665,7 @@
         <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1652,7 +1676,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
         <v>44</v>
@@ -1670,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1681,7 +1705,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
         <v>44</v>
@@ -1699,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="I23" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1710,7 +1734,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
         <v>44</v>
@@ -1728,7 +1752,7 @@
         <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1739,7 +1763,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>44</v>
@@ -1757,7 +1781,7 @@
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1768,7 +1792,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
         <v>44</v>
@@ -1786,7 +1810,7 @@
         <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -1797,7 +1821,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>44</v>
@@ -1815,7 +1839,7 @@
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -1826,7 +1850,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
         <v>44</v>
@@ -1844,7 +1868,7 @@
         <v>10</v>
       </c>
       <c r="I28" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -1855,7 +1879,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>44</v>
@@ -1873,7 +1897,7 @@
         <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -1884,7 +1908,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
         <v>44</v>
@@ -1902,7 +1926,7 @@
         <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -1913,7 +1937,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
         <v>44</v>
@@ -1931,7 +1955,7 @@
         <v>25</v>
       </c>
       <c r="I31" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -1942,7 +1966,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
         <v>44</v>
@@ -1960,7 +1984,7 @@
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -1971,7 +1995,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>44</v>
@@ -1989,7 +2013,7 @@
         <v>10</v>
       </c>
       <c r="I33" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -2000,7 +2024,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
@@ -2018,7 +2042,7 @@
         <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -2029,7 +2053,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
         <v>44</v>
@@ -2047,7 +2071,7 @@
         <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -2058,7 +2082,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
         <v>44</v>
@@ -2076,7 +2100,7 @@
         <v>25</v>
       </c>
       <c r="I36" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -2087,7 +2111,7 @@
         <v>26</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
         <v>44</v>
@@ -2105,7 +2129,7 @@
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -2116,7 +2140,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
         <v>44</v>
@@ -2134,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -2145,7 +2169,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
         <v>44</v>
@@ -2163,7 +2187,7 @@
         <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -2174,7 +2198,7 @@
         <v>26</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D40" t="s">
         <v>44</v>
@@ -2192,7 +2216,7 @@
         <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -2203,7 +2227,7 @@
         <v>26</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D41" t="s">
         <v>44</v>
@@ -2221,7 +2245,7 @@
         <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2309,7 +2333,7 @@
         <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -2341,7 +2365,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>37</v>
@@ -2443,7 +2467,7 @@
         <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B2A95D-4E23-4DE0-B6EE-D7A2E24930FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C72863-7384-40D1-8C91-AD46F09CE1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="125">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -442,6 +442,42 @@
   </si>
   <si>
     <t>모든 원거리 유닛의 체력 25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>descriptionForGuide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 공격력 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 체력 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 이동 속도 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 오라 범위 10/20/30/40/50% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 공격력 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 근거리 유닛의 체력 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 공격력 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 원거리 유닛의 체력 5/10/15/20/25% 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -826,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C904823C-220B-462B-9A10-524F2CEAD5FF}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -842,7 +878,7 @@
     <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -864,8 +900,11 @@
       <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="214.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>8010001</v>
       </c>
@@ -887,8 +926,11 @@
       <c r="G2" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>8010002</v>
       </c>
@@ -910,8 +952,11 @@
       <c r="G3" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="214.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>8010003</v>
       </c>
@@ -933,8 +978,11 @@
       <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="198" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>8010004</v>
       </c>
@@ -956,8 +1004,11 @@
       <c r="G5" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>8010005</v>
       </c>
@@ -979,14 +1030,17 @@
       <c r="G6" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
     </row>
   </sheetData>
@@ -1043,6 +1097,9 @@
       <c r="I1" t="s">
         <v>62</v>
       </c>
+      <c r="J1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
@@ -1071,6 +1128,9 @@
       </c>
       <c r="I2" t="s">
         <v>68</v>
+      </c>
+      <c r="J2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1205,7 +1265,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>80200021</v>
       </c>
@@ -1233,7 +1293,9 @@
       <c r="I7" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1370,7 +1432,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="99" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>80200031</v>
       </c>
@@ -1398,7 +1460,9 @@
       <c r="I12" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1523,7 +1587,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>80200041</v>
       </c>
@@ -1551,8 +1615,11 @@
       <c r="I17" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>80200042</v>
       </c>
@@ -1581,7 +1648,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>80200043</v>
       </c>
@@ -1610,7 +1677,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>80200044</v>
       </c>
@@ -1639,7 +1706,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>80200045</v>
       </c>
@@ -1668,7 +1735,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>80200051</v>
       </c>
@@ -1696,8 +1763,11 @@
       <c r="I22" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>80200052</v>
       </c>
@@ -1726,7 +1796,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>80200053</v>
       </c>
@@ -1755,7 +1825,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>80200054</v>
       </c>
@@ -1784,7 +1854,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>80200055</v>
       </c>
@@ -1813,7 +1883,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>80200061</v>
       </c>
@@ -1841,8 +1911,11 @@
       <c r="I27" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>80200062</v>
       </c>
@@ -1871,7 +1944,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>80200063</v>
       </c>
@@ -1900,7 +1973,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>80200064</v>
       </c>
@@ -1929,7 +2002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>80200065</v>
       </c>
@@ -1958,7 +2031,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>80200071</v>
       </c>
@@ -1986,8 +2059,11 @@
       <c r="I32" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>80200072</v>
       </c>
@@ -2016,7 +2092,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>80200073</v>
       </c>
@@ -2045,7 +2121,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>80200074</v>
       </c>
@@ -2074,7 +2150,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>80200075</v>
       </c>
@@ -2103,7 +2179,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>80200081</v>
       </c>
@@ -2131,8 +2207,11 @@
       <c r="I37" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>80200082</v>
       </c>
@@ -2161,7 +2240,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>80200083</v>
       </c>
@@ -2190,7 +2269,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>80200084</v>
       </c>
@@ -2219,7 +2298,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>80200085</v>
       </c>

--- a/Assets/Excel/ArtifactSO.xlsx
+++ b/Assets/Excel/ArtifactSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C72863-7384-40D1-8C91-AD46F09CE1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0790A7-CE8C-4F86-A451-35481AC44AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2DCCF674-CAD7-453F-824C-C429D706D6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="activeArtifacts" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="130">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -478,6 +478,26 @@
   </si>
   <si>
     <t>모든 원거리 유닛의 체력 5/10/15/20/25% 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5초 동안 모든 아군 유닛의 공격력이 15%만큼 증가하고, 공격 속도가 10% 빨라집니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 시전 3초 후, 빛의 기둥이 내려와 모든 아군 유닛의 체력을 최대 체력의 20%만큼 즉시 회복 시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 앞에 25초동안 높은 체력을 가진 수호 전령을 소환합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 전방 범위의 적들에게 (플레이어 공격력의 200%)의 광역 피해를 주고, 15초 동안 이동 속도와 공격 속도를 15% 감소 시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면의 모든 적 유닛에게 (플레이어 공격력의 60%)의 피해를 주는 번개를 5회에 걸쳐 내리칩니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -872,7 +892,7 @@
     <col min="5" max="5" width="17.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="46.75" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="67.375" customWidth="1"/>
     <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
@@ -904,7 +924,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="214.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>8010001</v>
       </c>
@@ -927,10 +947,10 @@
         <v>63</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>8010002</v>
       </c>
@@ -953,10 +973,10 @@
         <v>64</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="214.5" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>8010003</v>
       </c>
@@ -979,10 +999,10 @@
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="198" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>8010004</v>
       </c>
@@ -1005,10 +1025,10 @@
         <v>66</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>8010005</v>
       </c>
@@ -1031,7 +1051,7 @@
         <v>67</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
